--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Outros\Programas\HTML - Calculadora Marketplace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48DAB1D-309D-4337-B275-AA44EC3809BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845B7971-02FA-4511-A2C6-2C2ACA762A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15303,11 +15303,11 @@
         <v>482</v>
       </c>
       <c r="C619" s="10">
-        <v>104.04</v>
+        <v>98.4</v>
       </c>
       <c r="D619" s="8">
         <f t="shared" si="9"/>
-        <v>208.08</v>
+        <v>196.8</v>
       </c>
       <c r="E619" s="12" t="s">
         <v>1256</v>
